--- a/doc_testbed/Target_v13e_pre-deployment-tests.xlsx
+++ b/doc_testbed/Target_v13e_pre-deployment-tests.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hans\Documents\GitHub\shepherd_v2_planning\doc_testbed\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7ED8B6B5-37FC-47CE-A5A3-C40FED4B76C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41389EBC-6C64-4626-87AF-C0B0FDB46D5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="26172" yWindow="1464" windowWidth="15156" windowHeight="23088" xr2:uid="{0961F1A4-98B1-4F35-911A-F9CB780BF838}"/>
+    <workbookView xWindow="588" yWindow="0" windowWidth="19632" windowHeight="25296" xr2:uid="{0961F1A4-98B1-4F35-911A-F9CB780BF838}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -669,7 +669,7 @@
     <col min="6" max="6" width="7.6640625" customWidth="1"/>
     <col min="7" max="7" width="10.5546875" customWidth="1"/>
     <col min="8" max="8" width="10" customWidth="1"/>
-    <col min="9" max="9" width="24" customWidth="1"/>
+    <col min="9" max="9" width="26.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -891,7 +891,7 @@
       <c r="H9" s="1"/>
       <c r="I9" s="2"/>
     </row>
-    <row r="10" spans="1:9" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
         <v>18</v>
       </c>
@@ -1398,7 +1398,7 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="75" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="74" orientation="portrait" r:id="rId1"/>
   <tableParts count="1">
     <tablePart r:id="rId2"/>
   </tableParts>
